--- a/Data/cand_genes_gggenes_input.xlsx
+++ b/Data/cand_genes_gggenes_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madisonplunkert/Documents/GitHub/Stamen-loss-2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177C050C-0B37-9E40-891F-EDB12B547DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EB40DA-B253-1F4E-9DC1-96B4226ED6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="740" windowWidth="27240" windowHeight="15900" activeTab="1" xr2:uid="{AD06699C-2A77-9E41-8FF3-B4ABA5C1A4C4}"/>
+    <workbookView xWindow="2140" yWindow="660" windowWidth="27260" windowHeight="15920" xr2:uid="{AD06699C-2A77-9E41-8FF3-B4ABA5C1A4C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Genes" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_Hlk218602350" localSheetId="0">Genes!$A$9</definedName>
   </definedNames>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="32">
   <si>
     <t>feature</t>
   </si>
@@ -111,12 +111,6 @@
     <t>5@7.7</t>
   </si>
   <si>
-    <t>5@2.8</t>
-  </si>
-  <si>
-    <t>5@9.8</t>
-  </si>
-  <si>
     <t>forward</t>
   </si>
   <si>
@@ -139,6 +133,9 @@
   </si>
   <si>
     <t>indel</t>
+  </si>
+  <si>
+    <t>5@3.0</t>
   </si>
 </sst>
 </file>
@@ -198,12 +195,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34D66A35-D5F1-064B-8B43-B3D844B48A5C}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="15.1640625" customWidth="1"/>
@@ -579,7 +577,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -596,10 +594,10 @@
         <v>1515166</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -619,7 +617,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -639,7 +637,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -656,10 +654,10 @@
         <v>2202158</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -679,7 +677,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -699,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -716,10 +714,10 @@
         <v>2396329</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -736,10 +734,10 @@
         <v>2448584</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -756,10 +754,10 @@
         <v>2451796</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -779,7 +777,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -796,10 +794,10 @@
         <v>2972222</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -819,7 +817,7 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -836,52 +834,32 @@
         <v>2900000</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="A16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3">
+        <v>476540</v>
+      </c>
+      <c r="C16" s="3">
+        <v>872097</v>
+      </c>
+      <c r="D16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3">
-        <v>872097</v>
-      </c>
-      <c r="C16">
-        <v>1213621</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>25</v>
       </c>
-      <c r="E16" t="s">
-        <v>27</v>
-      </c>
       <c r="F16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17">
-        <v>2167867</v>
-      </c>
-      <c r="C17">
-        <v>3500000</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" t="s">
         <v>21</v>
       </c>
     </row>
@@ -897,7 +875,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -908,7 +886,7 @@
         <v>870885</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -916,7 +894,7 @@
         <v>870895</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -924,7 +902,7 @@
         <v>871312</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -932,7 +910,7 @@
         <v>871404</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -940,7 +918,7 @@
         <v>872035</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -948,7 +926,7 @@
         <v>873097</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -956,7 +934,7 @@
         <v>873180</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -964,7 +942,7 @@
         <v>873222</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -972,7 +950,7 @@
         <v>873464</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -980,7 +958,7 @@
         <v>873622</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -988,7 +966,7 @@
         <v>873739</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -996,7 +974,7 @@
         <v>873810</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1004,7 +982,7 @@
         <v>873919</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1012,7 +990,7 @@
         <v>873932</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1020,7 +998,7 @@
         <v>874509</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1028,7 +1006,7 @@
         <v>895696</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1036,7 +1014,7 @@
         <v>895756</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1044,7 +1022,7 @@
         <v>904183</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1052,7 +1030,7 @@
         <v>904562</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1060,7 +1038,7 @@
         <v>905812</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1068,7 +1046,7 @@
         <v>907051</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1076,7 +1054,7 @@
         <v>925118</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1084,7 +1062,7 @@
         <v>925340</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1092,7 +1070,7 @@
         <v>925482</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1100,7 +1078,7 @@
         <v>944530</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1108,7 +1086,7 @@
         <v>946082</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1116,7 +1094,7 @@
         <v>946204</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1124,7 +1102,7 @@
         <v>951427</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1132,7 +1110,7 @@
         <v>952885</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1140,7 +1118,7 @@
         <v>952903</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1148,7 +1126,7 @@
         <v>952997</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1156,7 +1134,7 @@
         <v>954847</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1164,7 +1142,7 @@
         <v>957093</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1172,7 +1150,7 @@
         <v>979499</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1180,7 +1158,7 @@
         <v>979556</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1188,7 +1166,7 @@
         <v>979595</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1196,7 +1174,7 @@
         <v>982305</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1204,7 +1182,7 @@
         <v>987588</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1212,7 +1190,7 @@
         <v>987727</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1220,7 +1198,7 @@
         <v>987729</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1228,7 +1206,7 @@
         <v>987731</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1236,7 +1214,7 @@
         <v>987953</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1244,7 +1222,7 @@
         <v>1006759</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1252,7 +1230,7 @@
         <v>1007279</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1260,7 +1238,7 @@
         <v>1009801</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1268,7 +1246,7 @@
         <v>1010912</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1276,7 +1254,7 @@
         <v>1025970</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1284,7 +1262,7 @@
         <v>1025988</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1292,7 +1270,7 @@
         <v>1026860</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1300,7 +1278,7 @@
         <v>1027768</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1308,7 +1286,7 @@
         <v>1027856</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1316,7 +1294,7 @@
         <v>1027879</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1324,7 +1302,7 @@
         <v>1028010</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1332,7 +1310,7 @@
         <v>1028047</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1340,7 +1318,7 @@
         <v>1028055</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1348,7 +1326,7 @@
         <v>1028068</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1356,7 +1334,7 @@
         <v>1034946</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1364,7 +1342,7 @@
         <v>1037986</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1372,7 +1350,7 @@
         <v>1042825</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1380,7 +1358,7 @@
         <v>1043078</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1388,7 +1366,7 @@
         <v>1043257</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1396,7 +1374,7 @@
         <v>1057994</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1404,7 +1382,7 @@
         <v>1058292</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1412,7 +1390,7 @@
         <v>1063779</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1420,7 +1398,7 @@
         <v>1067099</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1428,7 +1406,7 @@
         <v>1067700</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1436,7 +1414,7 @@
         <v>1067875</v>
       </c>
       <c r="B68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1444,7 +1422,7 @@
         <v>1075634</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1452,7 +1430,7 @@
         <v>1086960</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1460,7 +1438,7 @@
         <v>1086966</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1468,7 +1446,7 @@
         <v>1086975</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1476,7 +1454,7 @@
         <v>1086989</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1484,7 +1462,7 @@
         <v>1086998</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1492,7 +1470,7 @@
         <v>1087007</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1500,7 +1478,7 @@
         <v>1089983</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1508,7 +1486,7 @@
         <v>1090011</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1516,7 +1494,7 @@
         <v>1093816</v>
       </c>
       <c r="B78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1524,7 +1502,7 @@
         <v>1115681</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1532,7 +1510,7 @@
         <v>1120842</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1540,7 +1518,7 @@
         <v>1121676</v>
       </c>
       <c r="B81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1548,7 +1526,7 @@
         <v>1122228</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1556,7 +1534,7 @@
         <v>1122250</v>
       </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1564,7 +1542,7 @@
         <v>1125207</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1572,7 +1550,7 @@
         <v>1140087</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1580,7 +1558,7 @@
         <v>1144727</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1588,7 +1566,7 @@
         <v>1144735</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1596,7 +1574,7 @@
         <v>1144779</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1604,7 +1582,7 @@
         <v>1144785</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1612,7 +1590,7 @@
         <v>1144788</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1620,7 +1598,7 @@
         <v>1145091</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1628,7 +1606,7 @@
         <v>1145299</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1636,7 +1614,7 @@
         <v>1161376</v>
       </c>
       <c r="B93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1644,7 +1622,7 @@
         <v>1178659</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1652,7 +1630,7 @@
         <v>1178847</v>
       </c>
       <c r="B95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1660,7 +1638,7 @@
         <v>1179201</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1668,7 +1646,7 @@
         <v>1179546</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1676,7 +1654,7 @@
         <v>1180575</v>
       </c>
       <c r="B98" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1684,7 +1662,7 @@
         <v>1180639</v>
       </c>
       <c r="B99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1692,7 +1670,7 @@
         <v>1180819</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1700,7 +1678,7 @@
         <v>1180841</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1708,7 +1686,7 @@
         <v>1180875</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1716,7 +1694,7 @@
         <v>1181206</v>
       </c>
       <c r="B103" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1724,7 +1702,7 @@
         <v>1181356</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1732,7 +1710,7 @@
         <v>1188715</v>
       </c>
       <c r="B105" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1740,7 +1718,7 @@
         <v>1188749</v>
       </c>
       <c r="B106" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1748,7 +1726,7 @@
         <v>1190197</v>
       </c>
       <c r="B107" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1756,7 +1734,7 @@
         <v>1190270</v>
       </c>
       <c r="B108" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1764,7 +1742,7 @@
         <v>1190297</v>
       </c>
       <c r="B109" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1772,7 +1750,7 @@
         <v>1190298</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1780,7 +1758,7 @@
         <v>1190316</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1788,7 +1766,7 @@
         <v>1190384</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1796,7 +1774,7 @@
         <v>1190592</v>
       </c>
       <c r="B113" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1804,7 +1782,7 @@
         <v>1190627</v>
       </c>
       <c r="B114" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1812,7 +1790,7 @@
         <v>1190658</v>
       </c>
       <c r="B115" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1820,7 +1798,7 @@
         <v>1190665</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1828,7 +1806,7 @@
         <v>1190674</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1836,7 +1814,7 @@
         <v>1190679</v>
       </c>
       <c r="B118" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1844,7 +1822,7 @@
         <v>1190681</v>
       </c>
       <c r="B119" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1852,7 +1830,7 @@
         <v>1191104</v>
       </c>
       <c r="B120" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1860,7 +1838,7 @@
         <v>1191183</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1868,7 +1846,7 @@
         <v>1197316</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1876,7 +1854,7 @@
         <v>1208671</v>
       </c>
       <c r="B123" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1884,7 +1862,7 @@
         <v>1267856</v>
       </c>
       <c r="B124" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1892,7 +1870,7 @@
         <v>1282105</v>
       </c>
       <c r="B125" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -1900,7 +1878,7 @@
         <v>1282107</v>
       </c>
       <c r="B126" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -1908,7 +1886,7 @@
         <v>1282115</v>
       </c>
       <c r="B127" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -1916,7 +1894,7 @@
         <v>1282119</v>
       </c>
       <c r="B128" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -1924,7 +1902,7 @@
         <v>1282121</v>
       </c>
       <c r="B129" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -1932,7 +1910,7 @@
         <v>1282129</v>
       </c>
       <c r="B130" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -1940,7 +1918,7 @@
         <v>1282145</v>
       </c>
       <c r="B131" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -1948,7 +1926,7 @@
         <v>1359537</v>
       </c>
       <c r="B132" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -1956,7 +1934,7 @@
         <v>1361326</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -1964,7 +1942,7 @@
         <v>1365463</v>
       </c>
       <c r="B134" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -1972,7 +1950,7 @@
         <v>1365605</v>
       </c>
       <c r="B135" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1980,7 +1958,7 @@
         <v>1374464</v>
       </c>
       <c r="B136" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -1988,7 +1966,7 @@
         <v>1381183</v>
       </c>
       <c r="B137" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -1996,7 +1974,7 @@
         <v>1387050</v>
       </c>
       <c r="B138" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2004,7 +1982,7 @@
         <v>1396709</v>
       </c>
       <c r="B139" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2012,7 +1990,7 @@
         <v>1397925</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2020,7 +1998,7 @@
         <v>1397926</v>
       </c>
       <c r="B141" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2028,7 +2006,7 @@
         <v>1398157</v>
       </c>
       <c r="B142" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2036,7 +2014,7 @@
         <v>1398160</v>
       </c>
       <c r="B143" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2044,7 +2022,7 @@
         <v>1398321</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2052,7 +2030,7 @@
         <v>1398368</v>
       </c>
       <c r="B145" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2060,7 +2038,7 @@
         <v>1398517</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2068,7 +2046,7 @@
         <v>1398571</v>
       </c>
       <c r="B147" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2076,7 +2054,7 @@
         <v>1400816</v>
       </c>
       <c r="B148" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2084,7 +2062,7 @@
         <v>1409983</v>
       </c>
       <c r="B149" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2092,7 +2070,7 @@
         <v>1416298</v>
       </c>
       <c r="B150" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2100,7 +2078,7 @@
         <v>1420730</v>
       </c>
       <c r="B151" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2108,7 +2086,7 @@
         <v>1495761</v>
       </c>
       <c r="B152" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2116,7 +2094,7 @@
         <v>1495798</v>
       </c>
       <c r="B153" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2124,7 +2102,7 @@
         <v>1495864</v>
       </c>
       <c r="B154" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2132,7 +2110,7 @@
         <v>1504398</v>
       </c>
       <c r="B155" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2140,7 +2118,7 @@
         <v>1505084</v>
       </c>
       <c r="B156" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2148,7 +2126,7 @@
         <v>1509528</v>
       </c>
       <c r="B157" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2156,7 +2134,7 @@
         <v>1509597</v>
       </c>
       <c r="B158" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2164,7 +2142,7 @@
         <v>1509614</v>
       </c>
       <c r="B159" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2172,7 +2150,7 @@
         <v>1509618</v>
       </c>
       <c r="B160" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2180,7 +2158,7 @@
         <v>1509669</v>
       </c>
       <c r="B161" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2188,7 +2166,7 @@
         <v>1509679</v>
       </c>
       <c r="B162" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2196,7 +2174,7 @@
         <v>1509685</v>
       </c>
       <c r="B163" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2204,7 +2182,7 @@
         <v>1509703</v>
       </c>
       <c r="B164" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2212,7 +2190,7 @@
         <v>1509735</v>
       </c>
       <c r="B165" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2220,7 +2198,7 @@
         <v>1510416</v>
       </c>
       <c r="B166" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2228,7 +2206,7 @@
         <v>1511043</v>
       </c>
       <c r="B167" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2236,7 +2214,7 @@
         <v>1511091</v>
       </c>
       <c r="B168" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2244,7 +2222,7 @@
         <v>1511665</v>
       </c>
       <c r="B169" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2252,7 +2230,7 @@
         <v>1511941</v>
       </c>
       <c r="B170" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2260,7 +2238,7 @@
         <v>1512088</v>
       </c>
       <c r="B171" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2268,7 +2246,7 @@
         <v>1512216</v>
       </c>
       <c r="B172" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2276,7 +2254,7 @@
         <v>1512568</v>
       </c>
       <c r="B173" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2284,7 +2262,7 @@
         <v>1515095</v>
       </c>
       <c r="B174" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2292,7 +2270,7 @@
         <v>1569158</v>
       </c>
       <c r="B175" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2300,7 +2278,7 @@
         <v>1569170</v>
       </c>
       <c r="B176" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2308,7 +2286,7 @@
         <v>1569194</v>
       </c>
       <c r="B177" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2316,7 +2294,7 @@
         <v>1569218</v>
       </c>
       <c r="B178" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2324,7 +2302,7 @@
         <v>1569227</v>
       </c>
       <c r="B179" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2332,7 +2310,7 @@
         <v>1569246</v>
       </c>
       <c r="B180" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2340,7 +2318,7 @@
         <v>1569330</v>
       </c>
       <c r="B181" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2348,7 +2326,7 @@
         <v>1569395</v>
       </c>
       <c r="B182" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2356,7 +2334,7 @@
         <v>1569439</v>
       </c>
       <c r="B183" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2364,7 +2342,7 @@
         <v>1569446</v>
       </c>
       <c r="B184" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2372,7 +2350,7 @@
         <v>1569457</v>
       </c>
       <c r="B185" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2380,7 +2358,7 @@
         <v>1569463</v>
       </c>
       <c r="B186" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2388,7 +2366,7 @@
         <v>1569475</v>
       </c>
       <c r="B187" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2396,7 +2374,7 @@
         <v>1569481</v>
       </c>
       <c r="B188" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2404,7 +2382,7 @@
         <v>1569487</v>
       </c>
       <c r="B189" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2412,7 +2390,7 @@
         <v>1569511</v>
       </c>
       <c r="B190" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2420,7 +2398,7 @@
         <v>1610302</v>
       </c>
       <c r="B191" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -2428,7 +2406,7 @@
         <v>1610318</v>
       </c>
       <c r="B192" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -2436,7 +2414,7 @@
         <v>1610361</v>
       </c>
       <c r="B193" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -2444,7 +2422,7 @@
         <v>1616142</v>
       </c>
       <c r="B194" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -2452,7 +2430,7 @@
         <v>1616163</v>
       </c>
       <c r="B195" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -2460,7 +2438,7 @@
         <v>1619499</v>
       </c>
       <c r="B196" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -2468,7 +2446,7 @@
         <v>1622356</v>
       </c>
       <c r="B197" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -2476,7 +2454,7 @@
         <v>1639069</v>
       </c>
       <c r="B198" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -2484,7 +2462,7 @@
         <v>1641336</v>
       </c>
       <c r="B199" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -2492,7 +2470,7 @@
         <v>1643105</v>
       </c>
       <c r="B200" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -2500,7 +2478,7 @@
         <v>1646487</v>
       </c>
       <c r="B201" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -2508,7 +2486,7 @@
         <v>1647962</v>
       </c>
       <c r="B202" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -2516,7 +2494,7 @@
         <v>1653322</v>
       </c>
       <c r="B203" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -2524,7 +2502,7 @@
         <v>1656376</v>
       </c>
       <c r="B204" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -2532,7 +2510,7 @@
         <v>1656756</v>
       </c>
       <c r="B205" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -2540,7 +2518,7 @@
         <v>1666498</v>
       </c>
       <c r="B206" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -2548,7 +2526,7 @@
         <v>1667324</v>
       </c>
       <c r="B207" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -2556,7 +2534,7 @@
         <v>1667417</v>
       </c>
       <c r="B208" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -2564,7 +2542,7 @@
         <v>1667907</v>
       </c>
       <c r="B209" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -2572,7 +2550,7 @@
         <v>1667964</v>
       </c>
       <c r="B210" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -2580,7 +2558,7 @@
         <v>1669757</v>
       </c>
       <c r="B211" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -2588,7 +2566,7 @@
         <v>1669759</v>
       </c>
       <c r="B212" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -2596,7 +2574,7 @@
         <v>1669827</v>
       </c>
       <c r="B213" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -2604,7 +2582,7 @@
         <v>1670975</v>
       </c>
       <c r="B214" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -2612,7 +2590,7 @@
         <v>1740012</v>
       </c>
       <c r="B215" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -2620,7 +2598,7 @@
         <v>1760932</v>
       </c>
       <c r="B216" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -2628,7 +2606,7 @@
         <v>1793515</v>
       </c>
       <c r="B217" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -2636,7 +2614,7 @@
         <v>1796758</v>
       </c>
       <c r="B218" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -2644,7 +2622,7 @@
         <v>1834300</v>
       </c>
       <c r="B219" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -2652,7 +2630,7 @@
         <v>1868018</v>
       </c>
       <c r="B220" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -2660,7 +2638,7 @@
         <v>1917410</v>
       </c>
       <c r="B221" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -2668,7 +2646,7 @@
         <v>1917755</v>
       </c>
       <c r="B222" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -2676,7 +2654,7 @@
         <v>1918011</v>
       </c>
       <c r="B223" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -2684,7 +2662,7 @@
         <v>1918288</v>
       </c>
       <c r="B224" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -2692,7 +2670,7 @@
         <v>1927483</v>
       </c>
       <c r="B225" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -2700,7 +2678,7 @@
         <v>1928064</v>
       </c>
       <c r="B226" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -2708,7 +2686,7 @@
         <v>1936330</v>
       </c>
       <c r="B227" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -2716,7 +2694,7 @@
         <v>1937741</v>
       </c>
       <c r="B228" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -2724,7 +2702,7 @@
         <v>1950079</v>
       </c>
       <c r="B229" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -2732,7 +2710,7 @@
         <v>1951430</v>
       </c>
       <c r="B230" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -2740,7 +2718,7 @@
         <v>1951518</v>
       </c>
       <c r="B231" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -2748,7 +2726,7 @@
         <v>1956241</v>
       </c>
       <c r="B232" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -2756,7 +2734,7 @@
         <v>1959493</v>
       </c>
       <c r="B233" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -2764,7 +2742,7 @@
         <v>1971199</v>
       </c>
       <c r="B234" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -2772,7 +2750,7 @@
         <v>1974929</v>
       </c>
       <c r="B235" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -2780,7 +2758,7 @@
         <v>1976494</v>
       </c>
       <c r="B236" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -2788,7 +2766,7 @@
         <v>1977291</v>
       </c>
       <c r="B237" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -2796,7 +2774,7 @@
         <v>1977360</v>
       </c>
       <c r="B238" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -2804,7 +2782,7 @@
         <v>1979245</v>
       </c>
       <c r="B239" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -2812,7 +2790,7 @@
         <v>1994151</v>
       </c>
       <c r="B240" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -2820,7 +2798,7 @@
         <v>1995036</v>
       </c>
       <c r="B241" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -2828,7 +2806,7 @@
         <v>1995575</v>
       </c>
       <c r="B242" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -2836,7 +2814,7 @@
         <v>1995848</v>
       </c>
       <c r="B243" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -2844,7 +2822,7 @@
         <v>1998378</v>
       </c>
       <c r="B244" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -2852,7 +2830,7 @@
         <v>2004091</v>
       </c>
       <c r="B245" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -2860,7 +2838,7 @@
         <v>2021321</v>
       </c>
       <c r="B246" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -2868,7 +2846,7 @@
         <v>2029813</v>
       </c>
       <c r="B247" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -2876,7 +2854,7 @@
         <v>2034186</v>
       </c>
       <c r="B248" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -2884,7 +2862,7 @@
         <v>2037123</v>
       </c>
       <c r="B249" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -2892,7 +2870,7 @@
         <v>2038181</v>
       </c>
       <c r="B250" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -2900,7 +2878,7 @@
         <v>2038237</v>
       </c>
       <c r="B251" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -2908,7 +2886,7 @@
         <v>2038766</v>
       </c>
       <c r="B252" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -2916,7 +2894,7 @@
         <v>2039249</v>
       </c>
       <c r="B253" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -2924,7 +2902,7 @@
         <v>2060254</v>
       </c>
       <c r="B254" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -2932,7 +2910,7 @@
         <v>2071004</v>
       </c>
       <c r="B255" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -2940,7 +2918,7 @@
         <v>2071160</v>
       </c>
       <c r="B256" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -2948,7 +2926,7 @@
         <v>2071161</v>
       </c>
       <c r="B257" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -2956,7 +2934,7 @@
         <v>2071302</v>
       </c>
       <c r="B258" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -2964,7 +2942,7 @@
         <v>2071541</v>
       </c>
       <c r="B259" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -2972,7 +2950,7 @@
         <v>2071620</v>
       </c>
       <c r="B260" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -2980,7 +2958,7 @@
         <v>2071701</v>
       </c>
       <c r="B261" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -2988,7 +2966,7 @@
         <v>2071767</v>
       </c>
       <c r="B262" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -2996,7 +2974,7 @@
         <v>2071781</v>
       </c>
       <c r="B263" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3004,7 +2982,7 @@
         <v>2071802</v>
       </c>
       <c r="B264" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3012,7 +2990,7 @@
         <v>2071830</v>
       </c>
       <c r="B265" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3020,7 +2998,7 @@
         <v>2071980</v>
       </c>
       <c r="B266" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3028,7 +3006,7 @@
         <v>2072055</v>
       </c>
       <c r="B267" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3036,7 +3014,7 @@
         <v>2072179</v>
       </c>
       <c r="B268" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3044,7 +3022,7 @@
         <v>2072397</v>
       </c>
       <c r="B269" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3052,7 +3030,7 @@
         <v>2072430</v>
       </c>
       <c r="B270" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3060,7 +3038,7 @@
         <v>2072528</v>
       </c>
       <c r="B271" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3068,7 +3046,7 @@
         <v>2072580</v>
       </c>
       <c r="B272" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3076,7 +3054,7 @@
         <v>2072628</v>
       </c>
       <c r="B273" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3084,7 +3062,7 @@
         <v>2072994</v>
       </c>
       <c r="B274" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3092,7 +3070,7 @@
         <v>2073102</v>
       </c>
       <c r="B275" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3100,7 +3078,7 @@
         <v>2099424</v>
       </c>
       <c r="B276" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3108,7 +3086,7 @@
         <v>2099872</v>
       </c>
       <c r="B277" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3116,7 +3094,7 @@
         <v>2105886</v>
       </c>
       <c r="B278" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3124,7 +3102,7 @@
         <v>2105888</v>
       </c>
       <c r="B279" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3132,7 +3110,7 @@
         <v>2105890</v>
       </c>
       <c r="B280" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3140,7 +3118,7 @@
         <v>2105895</v>
       </c>
       <c r="B281" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3148,7 +3126,7 @@
         <v>2111365</v>
       </c>
       <c r="B282" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3156,7 +3134,7 @@
         <v>2118737</v>
       </c>
       <c r="B283" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3164,7 +3142,7 @@
         <v>2125050</v>
       </c>
       <c r="B284" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3172,7 +3150,7 @@
         <v>2173109</v>
       </c>
       <c r="B285" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3180,7 +3158,7 @@
         <v>2177772</v>
       </c>
       <c r="B286" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3188,7 +3166,7 @@
         <v>2177994</v>
       </c>
       <c r="B287" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3196,7 +3174,7 @@
         <v>2178001</v>
       </c>
       <c r="B288" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3204,7 +3182,7 @@
         <v>2178019</v>
       </c>
       <c r="B289" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3212,7 +3190,7 @@
         <v>2178042</v>
       </c>
       <c r="B290" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3220,7 +3198,7 @@
         <v>2178060</v>
       </c>
       <c r="B291" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3228,7 +3206,7 @@
         <v>2178067</v>
       </c>
       <c r="B292" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3236,7 +3214,7 @@
         <v>2178103</v>
       </c>
       <c r="B293" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3244,7 +3222,7 @@
         <v>2182055</v>
       </c>
       <c r="B294" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3252,7 +3230,7 @@
         <v>2182472</v>
       </c>
       <c r="B295" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3260,7 +3238,7 @@
         <v>2188855</v>
       </c>
       <c r="B296" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3268,7 +3246,7 @@
         <v>2194278</v>
       </c>
       <c r="B297" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3276,7 +3254,7 @@
         <v>2194417</v>
       </c>
       <c r="B298" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3284,7 +3262,7 @@
         <v>2194513</v>
       </c>
       <c r="B299" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3292,7 +3270,7 @@
         <v>2194568</v>
       </c>
       <c r="B300" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3300,7 +3278,7 @@
         <v>2194569</v>
       </c>
       <c r="B301" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3308,7 +3286,7 @@
         <v>2194650</v>
       </c>
       <c r="B302" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3316,7 +3294,7 @@
         <v>2195667</v>
       </c>
       <c r="B303" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3324,7 +3302,7 @@
         <v>2195673</v>
       </c>
       <c r="B304" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3332,7 +3310,7 @@
         <v>2195677</v>
       </c>
       <c r="B305" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3340,7 +3318,7 @@
         <v>2195693</v>
       </c>
       <c r="B306" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3348,7 +3326,7 @@
         <v>2195716</v>
       </c>
       <c r="B307" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3356,7 +3334,7 @@
         <v>2195731</v>
       </c>
       <c r="B308" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3364,7 +3342,7 @@
         <v>2195735</v>
       </c>
       <c r="B309" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3372,7 +3350,7 @@
         <v>2195738</v>
       </c>
       <c r="B310" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3380,7 +3358,7 @@
         <v>2200306</v>
       </c>
       <c r="B311" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3388,7 +3366,7 @@
         <v>2200433</v>
       </c>
       <c r="B312" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3396,7 +3374,7 @@
         <v>2200628</v>
       </c>
       <c r="B313" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3404,7 +3382,7 @@
         <v>2200646</v>
       </c>
       <c r="B314" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3412,7 +3390,7 @@
         <v>2200700</v>
       </c>
       <c r="B315" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -3420,7 +3398,7 @@
         <v>2200774</v>
       </c>
       <c r="B316" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -3428,7 +3406,7 @@
         <v>2200786</v>
       </c>
       <c r="B317" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -3436,7 +3414,7 @@
         <v>2201023</v>
       </c>
       <c r="B318" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -3444,7 +3422,7 @@
         <v>2201123</v>
       </c>
       <c r="B319" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -3452,7 +3430,7 @@
         <v>2201247</v>
       </c>
       <c r="B320" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -3460,7 +3438,7 @@
         <v>2201251</v>
       </c>
       <c r="B321" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -3468,7 +3446,7 @@
         <v>2201263</v>
       </c>
       <c r="B322" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -3476,7 +3454,7 @@
         <v>2201323</v>
       </c>
       <c r="B323" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -3484,7 +3462,7 @@
         <v>2201615</v>
       </c>
       <c r="B324" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -3492,7 +3470,7 @@
         <v>2215539</v>
       </c>
       <c r="B325" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -3500,7 +3478,7 @@
         <v>2219208</v>
       </c>
       <c r="B326" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -3508,7 +3486,7 @@
         <v>2219435</v>
       </c>
       <c r="B327" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -3516,7 +3494,7 @@
         <v>2220237</v>
       </c>
       <c r="B328" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -3524,7 +3502,7 @@
         <v>2220285</v>
       </c>
       <c r="B329" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -3532,7 +3510,7 @@
         <v>2220328</v>
       </c>
       <c r="B330" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -3540,7 +3518,7 @@
         <v>2220483</v>
       </c>
       <c r="B331" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -3548,7 +3526,7 @@
         <v>2220491</v>
       </c>
       <c r="B332" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -3556,7 +3534,7 @@
         <v>2220497</v>
       </c>
       <c r="B333" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -3564,7 +3542,7 @@
         <v>2239157</v>
       </c>
       <c r="B334" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -3572,7 +3550,7 @@
         <v>2240236</v>
       </c>
       <c r="B335" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -3580,7 +3558,7 @@
         <v>2245573</v>
       </c>
       <c r="B336" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -3588,7 +3566,7 @@
         <v>2245579</v>
       </c>
       <c r="B337" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -3596,7 +3574,7 @@
         <v>2348348</v>
       </c>
       <c r="B338" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -3604,7 +3582,7 @@
         <v>2348565</v>
       </c>
       <c r="B339" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -3612,7 +3590,7 @@
         <v>2362048</v>
       </c>
       <c r="B340" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -3620,7 +3598,7 @@
         <v>2362507</v>
       </c>
       <c r="B341" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -3628,7 +3606,7 @@
         <v>2362676</v>
       </c>
       <c r="B342" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -3636,7 +3614,7 @@
         <v>2362763</v>
       </c>
       <c r="B343" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -3644,7 +3622,7 @@
         <v>2377207</v>
       </c>
       <c r="B344" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -3652,7 +3630,7 @@
         <v>2380256</v>
       </c>
       <c r="B345" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -3660,7 +3638,7 @@
         <v>2385757</v>
       </c>
       <c r="B346" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -3668,7 +3646,7 @@
         <v>2386387</v>
       </c>
       <c r="B347" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -3676,7 +3654,7 @@
         <v>2388231</v>
       </c>
       <c r="B348" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -3684,7 +3662,7 @@
         <v>2388272</v>
       </c>
       <c r="B349" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -3692,7 +3670,7 @@
         <v>2388439</v>
       </c>
       <c r="B350" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -3700,7 +3678,7 @@
         <v>2388442</v>
       </c>
       <c r="B351" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -3708,7 +3686,7 @@
         <v>2395311</v>
       </c>
       <c r="B352" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -3716,7 +3694,7 @@
         <v>2398106</v>
       </c>
       <c r="B353" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -3724,7 +3702,7 @@
         <v>2404812</v>
       </c>
       <c r="B354" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -3732,7 +3710,7 @@
         <v>2435760</v>
       </c>
       <c r="B355" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -3740,7 +3718,7 @@
         <v>2440832</v>
       </c>
       <c r="B356" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -3748,7 +3726,7 @@
         <v>2446648</v>
       </c>
       <c r="B357" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -3756,7 +3734,7 @@
         <v>2448069</v>
       </c>
       <c r="B358" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -3764,7 +3742,7 @@
         <v>2448179</v>
       </c>
       <c r="B359" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -3772,7 +3750,7 @@
         <v>2448202</v>
       </c>
       <c r="B360" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -3780,7 +3758,7 @@
         <v>2448204</v>
       </c>
       <c r="B361" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -3788,7 +3766,7 @@
         <v>2448206</v>
       </c>
       <c r="B362" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -3796,7 +3774,7 @@
         <v>2448216</v>
       </c>
       <c r="B363" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -3804,7 +3782,7 @@
         <v>2448240</v>
       </c>
       <c r="B364" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -3812,7 +3790,7 @@
         <v>2448254</v>
       </c>
       <c r="B365" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -3820,7 +3798,7 @@
         <v>2448375</v>
       </c>
       <c r="B366" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -3828,7 +3806,7 @@
         <v>2448503</v>
       </c>
       <c r="B367" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -3836,7 +3814,7 @@
         <v>2448511</v>
       </c>
       <c r="B368" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -3844,7 +3822,7 @@
         <v>2448515</v>
       </c>
       <c r="B369" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -3852,7 +3830,7 @@
         <v>2448532</v>
       </c>
       <c r="B370" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -3860,7 +3838,7 @@
         <v>2448545</v>
       </c>
       <c r="B371" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -3868,7 +3846,7 @@
         <v>2448617</v>
       </c>
       <c r="B372" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -3876,7 +3854,7 @@
         <v>2448732</v>
       </c>
       <c r="B373" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -3884,7 +3862,7 @@
         <v>2448744</v>
       </c>
       <c r="B374" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -3892,7 +3870,7 @@
         <v>2448774</v>
       </c>
       <c r="B375" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -3900,7 +3878,7 @@
         <v>2448841</v>
       </c>
       <c r="B376" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -3908,7 +3886,7 @@
         <v>2448842</v>
       </c>
       <c r="B377" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -3916,7 +3894,7 @@
         <v>2448852</v>
       </c>
       <c r="B378" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -3924,7 +3902,7 @@
         <v>2448973</v>
       </c>
       <c r="B379" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -3932,7 +3910,7 @@
         <v>2449014</v>
       </c>
       <c r="B380" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -3940,7 +3918,7 @@
         <v>2449018</v>
       </c>
       <c r="B381" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -3948,7 +3926,7 @@
         <v>2449055</v>
       </c>
       <c r="B382" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -3956,7 +3934,7 @@
         <v>2449058</v>
       </c>
       <c r="B383" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -3964,7 +3942,7 @@
         <v>2449086</v>
       </c>
       <c r="B384" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -3972,7 +3950,7 @@
         <v>2449104</v>
       </c>
       <c r="B385" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -3980,7 +3958,7 @@
         <v>2449131</v>
       </c>
       <c r="B386" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -3988,7 +3966,7 @@
         <v>2449165</v>
       </c>
       <c r="B387" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -3996,7 +3974,7 @@
         <v>2449221</v>
       </c>
       <c r="B388" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -4004,7 +3982,7 @@
         <v>2451940</v>
       </c>
       <c r="B389" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -4012,7 +3990,7 @@
         <v>2451985</v>
       </c>
       <c r="B390" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -4020,7 +3998,7 @@
         <v>2461524</v>
       </c>
       <c r="B391" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -4028,7 +4006,7 @@
         <v>2467579</v>
       </c>
       <c r="B392" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -4036,7 +4014,7 @@
         <v>2482587</v>
       </c>
       <c r="B393" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -4044,7 +4022,7 @@
         <v>2501749</v>
       </c>
       <c r="B394" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -4052,7 +4030,7 @@
         <v>2603316</v>
       </c>
       <c r="B395" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -4060,7 +4038,7 @@
         <v>2603384</v>
       </c>
       <c r="B396" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -4068,7 +4046,7 @@
         <v>2605100</v>
       </c>
       <c r="B397" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -4076,7 +4054,7 @@
         <v>2611770</v>
       </c>
       <c r="B398" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -4084,7 +4062,7 @@
         <v>2617262</v>
       </c>
       <c r="B399" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -4092,7 +4070,7 @@
         <v>2622625</v>
       </c>
       <c r="B400" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -4100,7 +4078,7 @@
         <v>2735041</v>
       </c>
       <c r="B401" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -4108,7 +4086,7 @@
         <v>2735439</v>
       </c>
       <c r="B402" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -4116,7 +4094,7 @@
         <v>2774541</v>
       </c>
       <c r="B403" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -4124,7 +4102,7 @@
         <v>2968297</v>
       </c>
       <c r="B404" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -4132,7 +4110,7 @@
         <v>2971801</v>
       </c>
       <c r="B405" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -4140,7 +4118,7 @@
         <v>3018601</v>
       </c>
       <c r="B406" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -4148,7 +4126,7 @@
         <v>3018795</v>
       </c>
       <c r="B407" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -4156,7 +4134,7 @@
         <v>3028995</v>
       </c>
       <c r="B408" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -4164,7 +4142,7 @@
         <v>3029190</v>
       </c>
       <c r="B409" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -4172,7 +4150,7 @@
         <v>3030605</v>
       </c>
       <c r="B410" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -4180,7 +4158,7 @@
         <v>3034912</v>
       </c>
       <c r="B411" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -4188,7 +4166,7 @@
         <v>3037581</v>
       </c>
       <c r="B412" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -4196,7 +4174,7 @@
         <v>3040124</v>
       </c>
       <c r="B413" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -4204,7 +4182,7 @@
         <v>3040187</v>
       </c>
       <c r="B414" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -4212,7 +4190,7 @@
         <v>3040280</v>
       </c>
       <c r="B415" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -4220,7 +4198,7 @@
         <v>3040353</v>
       </c>
       <c r="B416" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -4228,7 +4206,7 @@
         <v>3040432</v>
       </c>
       <c r="B417" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -4236,7 +4214,7 @@
         <v>3040443</v>
       </c>
       <c r="B418" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -4244,7 +4222,7 @@
         <v>3040449</v>
       </c>
       <c r="B419" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -4252,7 +4230,7 @@
         <v>3040578</v>
       </c>
       <c r="B420" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -4260,7 +4238,7 @@
         <v>3040601</v>
       </c>
       <c r="B421" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -4268,7 +4246,7 @@
         <v>3040603</v>
       </c>
       <c r="B422" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -4276,7 +4254,7 @@
         <v>3078536</v>
       </c>
       <c r="B423" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -4284,7 +4262,7 @@
         <v>3078999</v>
       </c>
       <c r="B424" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -4292,7 +4270,7 @@
         <v>3079133</v>
       </c>
       <c r="B425" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -4300,7 +4278,7 @@
         <v>3079328</v>
       </c>
       <c r="B426" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -4308,7 +4286,7 @@
         <v>3079706</v>
       </c>
       <c r="B427" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -4316,7 +4294,7 @@
         <v>3079734</v>
       </c>
       <c r="B428" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -4324,7 +4302,7 @@
         <v>3079815</v>
       </c>
       <c r="B429" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -4332,7 +4310,7 @@
         <v>3079906</v>
       </c>
       <c r="B430" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -4340,7 +4318,7 @@
         <v>3079914</v>
       </c>
       <c r="B431" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -4348,7 +4326,7 @@
         <v>3079930</v>
       </c>
       <c r="B432" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -4356,7 +4334,7 @@
         <v>3080422</v>
       </c>
       <c r="B433" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -4364,7 +4342,7 @@
         <v>3080446</v>
       </c>
       <c r="B434" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -4372,7 +4350,7 @@
         <v>3080620</v>
       </c>
       <c r="B435" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -4380,7 +4358,7 @@
         <v>3080811</v>
       </c>
       <c r="B436" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -4388,7 +4366,7 @@
         <v>3080824</v>
       </c>
       <c r="B437" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -4396,7 +4374,7 @@
         <v>3085551</v>
       </c>
       <c r="B438" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -4404,7 +4382,7 @@
         <v>3085934</v>
       </c>
       <c r="B439" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -4412,7 +4390,7 @@
         <v>3086814</v>
       </c>
       <c r="B440" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -4420,7 +4398,7 @@
         <v>3092943</v>
       </c>
       <c r="B441" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -4428,7 +4406,7 @@
         <v>3093532</v>
       </c>
       <c r="B442" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -4436,7 +4414,7 @@
         <v>3094080</v>
       </c>
       <c r="B443" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -4444,7 +4422,7 @@
         <v>3106963</v>
       </c>
       <c r="B444" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -4452,7 +4430,7 @@
         <v>3106968</v>
       </c>
       <c r="B445" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -4460,7 +4438,7 @@
         <v>3107919</v>
       </c>
       <c r="B446" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -4468,7 +4446,7 @@
         <v>3107988</v>
       </c>
       <c r="B447" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -4476,7 +4454,7 @@
         <v>3115128</v>
       </c>
       <c r="B448" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -4484,7 +4462,7 @@
         <v>3130529</v>
       </c>
       <c r="B449" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -4492,7 +4470,7 @@
         <v>3131996</v>
       </c>
       <c r="B450" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -4500,7 +4478,7 @@
         <v>3132164</v>
       </c>
       <c r="B451" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -4508,7 +4486,7 @@
         <v>3140591</v>
       </c>
       <c r="B452" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -4516,7 +4494,7 @@
         <v>3140625</v>
       </c>
       <c r="B453" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -4524,7 +4502,7 @@
         <v>3140694</v>
       </c>
       <c r="B454" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -4532,7 +4510,7 @@
         <v>3140765</v>
       </c>
       <c r="B455" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -4540,7 +4518,7 @@
         <v>3142080</v>
       </c>
       <c r="B456" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -4548,7 +4526,7 @@
         <v>3145777</v>
       </c>
       <c r="B457" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -4556,7 +4534,7 @@
         <v>3145778</v>
       </c>
       <c r="B458" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -4564,7 +4542,7 @@
         <v>3145779</v>
       </c>
       <c r="B459" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -4572,7 +4550,7 @@
         <v>3153627</v>
       </c>
       <c r="B460" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -4580,7 +4558,7 @@
         <v>3161917</v>
       </c>
       <c r="B461" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -4588,7 +4566,7 @@
         <v>3173313</v>
       </c>
       <c r="B462" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -4596,7 +4574,7 @@
         <v>3178318</v>
       </c>
       <c r="B463" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -4604,7 +4582,7 @@
         <v>3181276</v>
       </c>
       <c r="B464" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -4612,7 +4590,7 @@
         <v>3181346</v>
       </c>
       <c r="B465" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -4620,7 +4598,7 @@
         <v>3185704</v>
       </c>
       <c r="B466" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -4628,7 +4606,7 @@
         <v>3185978</v>
       </c>
       <c r="B467" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -4636,7 +4614,7 @@
         <v>3188552</v>
       </c>
       <c r="B468" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -4644,7 +4622,7 @@
         <v>3190235</v>
       </c>
       <c r="B469" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -4652,7 +4630,7 @@
         <v>3191488</v>
       </c>
       <c r="B470" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -4660,7 +4638,7 @@
         <v>3192385</v>
       </c>
       <c r="B471" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -4668,7 +4646,7 @@
         <v>3192391</v>
       </c>
       <c r="B472" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -4676,7 +4654,7 @@
         <v>3192397</v>
       </c>
       <c r="B473" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -4684,7 +4662,7 @@
         <v>3193046</v>
       </c>
       <c r="B474" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -4692,7 +4670,7 @@
         <v>3194934</v>
       </c>
       <c r="B475" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -4700,7 +4678,7 @@
         <v>3195291</v>
       </c>
       <c r="B476" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -4708,7 +4686,7 @@
         <v>3196619</v>
       </c>
       <c r="B477" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -4716,7 +4694,7 @@
         <v>3203379</v>
       </c>
       <c r="B478" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -4724,7 +4702,7 @@
         <v>3203388</v>
       </c>
       <c r="B479" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -4732,7 +4710,7 @@
         <v>3203406</v>
       </c>
       <c r="B480" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -4740,7 +4718,7 @@
         <v>3203460</v>
       </c>
       <c r="B481" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -4748,7 +4726,7 @@
         <v>3203487</v>
       </c>
       <c r="B482" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -4756,7 +4734,7 @@
         <v>3203517</v>
       </c>
       <c r="B483" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -4764,7 +4742,7 @@
         <v>3203547</v>
       </c>
       <c r="B484" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -4772,7 +4750,7 @@
         <v>3203661</v>
       </c>
       <c r="B485" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -4780,7 +4758,7 @@
         <v>3203685</v>
       </c>
       <c r="B486" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -4788,7 +4766,7 @@
         <v>3203751</v>
       </c>
       <c r="B487" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -4796,7 +4774,7 @@
         <v>3203757</v>
       </c>
       <c r="B488" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -4804,7 +4782,7 @@
         <v>3209582</v>
       </c>
       <c r="B489" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -4812,7 +4790,7 @@
         <v>3209593</v>
       </c>
       <c r="B490" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -4820,7 +4798,7 @@
         <v>3220428</v>
       </c>
       <c r="B491" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -4828,7 +4806,7 @@
         <v>3221651</v>
       </c>
       <c r="B492" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -4836,7 +4814,7 @@
         <v>3222006</v>
       </c>
       <c r="B493" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -4844,7 +4822,7 @@
         <v>3223090</v>
       </c>
       <c r="B494" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -4852,7 +4830,7 @@
         <v>3223296</v>
       </c>
       <c r="B495" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -4860,7 +4838,7 @@
         <v>3225118</v>
       </c>
       <c r="B496" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -4868,7 +4846,7 @@
         <v>3234405</v>
       </c>
       <c r="B497" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -4876,7 +4854,7 @@
         <v>3234419</v>
       </c>
       <c r="B498" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -4884,7 +4862,7 @@
         <v>3234882</v>
       </c>
       <c r="B499" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -4892,7 +4870,7 @@
         <v>3237056</v>
       </c>
       <c r="B500" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -4900,7 +4878,7 @@
         <v>3240731</v>
       </c>
       <c r="B501" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -4908,7 +4886,7 @@
         <v>3242643</v>
       </c>
       <c r="B502" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -4916,7 +4894,7 @@
         <v>3246785</v>
       </c>
       <c r="B503" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -4924,7 +4902,7 @@
         <v>3247977</v>
       </c>
       <c r="B504" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -4932,7 +4910,7 @@
         <v>3250273</v>
       </c>
       <c r="B505" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -4940,7 +4918,7 @@
         <v>3250378</v>
       </c>
       <c r="B506" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -4948,7 +4926,7 @@
         <v>3256738</v>
       </c>
       <c r="B507" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -4956,7 +4934,7 @@
         <v>3272458</v>
       </c>
       <c r="B508" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -4964,7 +4942,7 @@
         <v>3314693</v>
       </c>
       <c r="B509" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -4972,7 +4950,7 @@
         <v>3315456</v>
       </c>
       <c r="B510" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -4980,7 +4958,7 @@
         <v>3316215</v>
       </c>
       <c r="B511" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -4988,7 +4966,7 @@
         <v>3340168</v>
       </c>
       <c r="B512" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -4996,7 +4974,7 @@
         <v>3340687</v>
       </c>
       <c r="B513" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -5004,7 +4982,7 @@
         <v>3340986</v>
       </c>
       <c r="B514" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -5012,7 +4990,7 @@
         <v>3343544</v>
       </c>
       <c r="B515" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -5020,7 +4998,7 @@
         <v>3343549</v>
       </c>
       <c r="B516" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -5028,7 +5006,7 @@
         <v>3432918</v>
       </c>
       <c r="B517" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -5036,7 +5014,7 @@
         <v>3466244</v>
       </c>
       <c r="B518" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -5044,7 +5022,7 @@
         <v>3473535</v>
       </c>
       <c r="B519" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -5052,7 +5030,7 @@
         <v>3473545</v>
       </c>
       <c r="B520" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -5060,7 +5038,7 @@
         <v>3474398</v>
       </c>
       <c r="B521" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -5068,7 +5046,7 @@
         <v>3475330</v>
       </c>
       <c r="B522" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -5076,7 +5054,7 @@
         <v>3482258</v>
       </c>
       <c r="B523" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -5084,7 +5062,7 @@
         <v>3482354</v>
       </c>
       <c r="B524" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -5092,7 +5070,7 @@
         <v>3482370</v>
       </c>
       <c r="B525" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -5100,7 +5078,7 @@
         <v>3482398</v>
       </c>
       <c r="B526" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -5108,7 +5086,7 @@
         <v>2195667</v>
       </c>
       <c r="B527" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -5116,7 +5094,7 @@
         <v>2195673</v>
       </c>
       <c r="B528" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -5124,7 +5102,7 @@
         <v>2195677</v>
       </c>
       <c r="B529" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -5132,7 +5110,7 @@
         <v>2195693</v>
       </c>
       <c r="B530" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -5140,7 +5118,7 @@
         <v>2195716</v>
       </c>
       <c r="B531" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -5148,7 +5126,7 @@
         <v>2195731</v>
       </c>
       <c r="B532" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -5156,10 +5134,10 @@
         <v>2195735</v>
       </c>
       <c r="B533" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C533" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -5167,10 +5145,10 @@
         <v>2195738</v>
       </c>
       <c r="B534" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C534" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -5178,7 +5156,7 @@
         <v>2200306</v>
       </c>
       <c r="B535" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -5186,7 +5164,7 @@
         <v>2200433</v>
       </c>
       <c r="B536" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -5194,7 +5172,7 @@
         <v>2200628</v>
       </c>
       <c r="B537" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -5202,7 +5180,7 @@
         <v>2200646</v>
       </c>
       <c r="B538" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -5210,7 +5188,7 @@
         <v>2200700</v>
       </c>
       <c r="B539" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -5218,7 +5196,7 @@
         <v>2200774</v>
       </c>
       <c r="B540" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -5226,7 +5204,7 @@
         <v>2200786</v>
       </c>
       <c r="B541" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -5234,7 +5212,7 @@
         <v>2201023</v>
       </c>
       <c r="B542" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -5242,7 +5220,7 @@
         <v>2201123</v>
       </c>
       <c r="B543" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -5250,10 +5228,10 @@
         <v>2201247</v>
       </c>
       <c r="B544" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C544" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -5261,10 +5239,10 @@
         <v>2201251</v>
       </c>
       <c r="B545" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C545" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -5272,7 +5250,7 @@
         <v>2201263</v>
       </c>
       <c r="B546" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -5280,7 +5258,7 @@
         <v>2201323</v>
       </c>
       <c r="B547" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -5288,7 +5266,7 @@
         <v>2201615</v>
       </c>
       <c r="B548" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -5296,7 +5274,7 @@
         <v>2448069</v>
       </c>
       <c r="B549" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -5304,7 +5282,7 @@
         <v>2448179</v>
       </c>
       <c r="B550" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -5312,7 +5290,7 @@
         <v>2448202</v>
       </c>
       <c r="B551" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -5320,7 +5298,7 @@
         <v>2448204</v>
       </c>
       <c r="B552" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -5328,7 +5306,7 @@
         <v>2448206</v>
       </c>
       <c r="B553" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -5336,7 +5314,7 @@
         <v>2448216</v>
       </c>
       <c r="B554" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -5344,7 +5322,7 @@
         <v>2448240</v>
       </c>
       <c r="B555" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -5352,7 +5330,7 @@
         <v>2448254</v>
       </c>
       <c r="B556" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -5360,7 +5338,7 @@
         <v>2448375</v>
       </c>
       <c r="B557" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -5368,7 +5346,7 @@
         <v>2448503</v>
       </c>
       <c r="B558" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -5376,10 +5354,10 @@
         <v>2448511</v>
       </c>
       <c r="B559" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C559" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -5387,7 +5365,7 @@
         <v>2448515</v>
       </c>
       <c r="B560" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -5395,7 +5373,7 @@
         <v>2448532</v>
       </c>
       <c r="B561" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -5403,7 +5381,7 @@
         <v>2448545</v>
       </c>
       <c r="B562" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -5411,10 +5389,10 @@
         <v>2448617</v>
       </c>
       <c r="B563" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C563" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -5422,7 +5400,7 @@
         <v>2448732</v>
       </c>
       <c r="B564" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -5430,7 +5408,7 @@
         <v>2448744</v>
       </c>
       <c r="B565" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -5438,10 +5416,10 @@
         <v>2448774</v>
       </c>
       <c r="B566" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C566" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -5449,7 +5427,7 @@
         <v>2448841</v>
       </c>
       <c r="B567" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -5457,7 +5435,7 @@
         <v>2448842</v>
       </c>
       <c r="B568" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -5465,7 +5443,7 @@
         <v>2448852</v>
       </c>
       <c r="B569" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -5473,10 +5451,10 @@
         <v>2448973</v>
       </c>
       <c r="B570" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C570" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -5484,7 +5462,7 @@
         <v>2449014</v>
       </c>
       <c r="B571" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -5492,7 +5470,7 @@
         <v>2449018</v>
       </c>
       <c r="B572" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -5500,7 +5478,7 @@
         <v>2449055</v>
       </c>
       <c r="B573" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -5508,10 +5486,10 @@
         <v>2449058</v>
       </c>
       <c r="B574" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C574" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -5519,7 +5497,7 @@
         <v>2449086</v>
       </c>
       <c r="B575" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -5527,7 +5505,7 @@
         <v>2449104</v>
       </c>
       <c r="B576" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -5535,7 +5513,7 @@
         <v>2449131</v>
       </c>
       <c r="B577" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -5543,7 +5521,7 @@
         <v>2449165</v>
       </c>
       <c r="B578" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -5551,7 +5529,7 @@
         <v>2449221</v>
       </c>
       <c r="B579" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -5559,7 +5537,7 @@
         <v>2451940</v>
       </c>
       <c r="B580" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -5567,7 +5545,7 @@
         <v>2451985</v>
       </c>
       <c r="B581" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
